--- a/Phenotype/Tables/EPS_TableS3A_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS3A_FromR.xlsx
@@ -394,27 +394,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.150</t>
+          <t>6.205</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.420</t>
+          <t>3.189</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25.457</t>
+          <t>33.279</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>1.945</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.060</t>
         </is>
       </c>
     </row>
@@ -426,27 +426,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13.210</t>
+          <t>13.961</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>3.811</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.393</t>
+          <t>18.000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.253</t>
+          <t>3.663</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.002</t>
         </is>
       </c>
     </row>
@@ -458,7 +458,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69.769</t>
+          <t>55.266</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.224 (χ²)</t>
+          <t>1.535 (χ²)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.215</t>
         </is>
       </c>
     </row>
